--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T3_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T3_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>49</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.36e+05</t>
-  </si>
-  <si>
-    <t>(87786.898)</t>
-  </si>
-  <si>
-    <t>498.554</t>
-  </si>
-  <si>
-    <t>(37.131)</t>
-  </si>
-  <si>
-    <t>3.745</t>
-  </si>
-  <si>
-    <t>(0.051)</t>
-  </si>
-  <si>
-    <t>5.180</t>
-  </si>
-  <si>
-    <t>(1.257)</t>
-  </si>
-  <si>
-    <t>86.625</t>
-  </si>
-  <si>
-    <t>(0.534)</t>
-  </si>
-  <si>
-    <t>8.67e+05</t>
-  </si>
-  <si>
-    <t>(58645.070)</t>
-  </si>
-  <si>
-    <t>2.049</t>
-  </si>
-  <si>
-    <t>(0.141)</t>
-  </si>
-  <si>
-    <t>2.100</t>
-  </si>
-  <si>
-    <t>(0.434)</t>
-  </si>
-  <si>
-    <t>29.260</t>
-  </si>
-  <si>
-    <t>(5.021)</t>
-  </si>
-  <si>
-    <t>0.920</t>
-  </si>
-  <si>
-    <t>(0.039)</t>
-  </si>
-  <si>
-    <t>66</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.73e+05</t>
-  </si>
-  <si>
-    <t>(93258.332)</t>
-  </si>
-  <si>
-    <t>488.152</t>
-  </si>
-  <si>
-    <t>(43.063)</t>
-  </si>
-  <si>
-    <t>3.346</t>
-  </si>
-  <si>
-    <t>(0.045)</t>
-  </si>
-  <si>
-    <t>24.242</t>
-  </si>
-  <si>
-    <t>(2.950)</t>
-  </si>
-  <si>
-    <t>91.387</t>
-  </si>
-  <si>
-    <t>(0.351)</t>
-  </si>
-  <si>
-    <t>1.36e+06</t>
-  </si>
-  <si>
-    <t>(54270.106)</t>
-  </si>
-  <si>
-    <t>3.327</t>
-  </si>
-  <si>
-    <t>(0.110)</t>
-  </si>
-  <si>
-    <t>5.909</t>
-  </si>
-  <si>
-    <t>(0.502)</t>
-  </si>
-  <si>
-    <t>42.864</t>
-  </si>
-  <si>
-    <t>(2.557)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.38e+05</t>
-  </si>
-  <si>
-    <t>-10.402</t>
-  </si>
-  <si>
-    <t>-0.399***</t>
-  </si>
-  <si>
-    <t>19.062***</t>
-  </si>
-  <si>
-    <t>4.763***</t>
-  </si>
-  <si>
-    <t>4.91e+05***</t>
-  </si>
-  <si>
-    <t>1.278***</t>
-  </si>
-  <si>
-    <t>3.809***</t>
-  </si>
-  <si>
-    <t>13.604**</t>
-  </si>
-  <si>
-    <t>0.080**</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T3_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T3_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>50</t>
+  </si>
+  <si>
+    <t>49</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.36e+05</t>
+  </si>
+  <si>
+    <t>(87786.898)</t>
+  </si>
+  <si>
+    <t>498.554</t>
+  </si>
+  <si>
+    <t>(37.131)</t>
+  </si>
+  <si>
+    <t>3.745</t>
+  </si>
+  <si>
+    <t>(0.051)</t>
+  </si>
+  <si>
+    <t>5.180</t>
+  </si>
+  <si>
+    <t>(1.257)</t>
+  </si>
+  <si>
+    <t>86.625</t>
+  </si>
+  <si>
+    <t>(0.534)</t>
+  </si>
+  <si>
+    <t>8.67e+05</t>
+  </si>
+  <si>
+    <t>(58645.070)</t>
+  </si>
+  <si>
+    <t>2.049</t>
+  </si>
+  <si>
+    <t>(0.141)</t>
+  </si>
+  <si>
+    <t>2.100</t>
+  </si>
+  <si>
+    <t>(0.434)</t>
+  </si>
+  <si>
+    <t>29.260</t>
+  </si>
+  <si>
+    <t>(5.021)</t>
+  </si>
+  <si>
+    <t>0.920</t>
+  </si>
+  <si>
+    <t>(0.039)</t>
+  </si>
+  <si>
+    <t>66</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>6.73e+05</t>
+  </si>
+  <si>
+    <t>(93258.332)</t>
+  </si>
+  <si>
+    <t>488.152</t>
+  </si>
+  <si>
+    <t>(43.063)</t>
+  </si>
+  <si>
+    <t>3.346</t>
+  </si>
+  <si>
+    <t>(0.045)</t>
+  </si>
+  <si>
+    <t>24.242</t>
+  </si>
+  <si>
+    <t>(2.950)</t>
+  </si>
+  <si>
+    <t>91.387</t>
+  </si>
+  <si>
+    <t>(0.351)</t>
+  </si>
+  <si>
+    <t>1.36e+06</t>
+  </si>
+  <si>
+    <t>(54270.106)</t>
+  </si>
+  <si>
+    <t>3.327</t>
+  </si>
+  <si>
+    <t>(0.110)</t>
+  </si>
+  <si>
+    <t>5.909</t>
+  </si>
+  <si>
+    <t>(0.502)</t>
+  </si>
+  <si>
+    <t>42.864</t>
+  </si>
+  <si>
+    <t>(2.557)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.38e+05</t>
+  </si>
+  <si>
+    <t>-10.402</t>
+  </si>
+  <si>
+    <t>-0.399***</t>
+  </si>
+  <si>
+    <t>19.062***</t>
+  </si>
+  <si>
+    <t>4.763***</t>
+  </si>
+  <si>
+    <t>4.91e+05***</t>
+  </si>
+  <si>
+    <t>1.278***</t>
+  </si>
+  <si>
+    <t>3.809***</t>
+  </si>
+  <si>
+    <t>13.604**</t>
+  </si>
+  <si>
+    <t>0.080**</t>
   </si>
 </sst>
 </file>
